--- a/docs/files/REPORT_FILTRI/Agente - CR BRAVI MATTEO.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR BRAVI MATTEO.xlsx
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>0</v>
